--- a/tests/workbooktests/workbooks/test_defaultprobability.xlsx
+++ b/tests/workbooktests/workbooks/test_defaultprobability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2052C86-9151-403F-B33C-E7D928CB6CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CA180B4-5CD0-46F2-83DA-FCC2AC1A2680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{A8EF8239-07AD-4029-BB02-2A7227351A4C}"/>
+    <workbookView xWindow="2940" yWindow="-20250" windowWidth="34665" windowHeight="18960" xr2:uid="{A8EF8239-07AD-4029-BB02-2A7227351A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="65">
   <si>
     <t>Evaluation date</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>qlRiskyBondEngine</t>
+  </si>
+  <si>
+    <t>trade_date</t>
   </si>
 </sst>
 </file>
@@ -656,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3D2CA1-C9FE-482C-87E0-D0F1966AB66D}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.6640625" bestFit="1" customWidth="1"/>
@@ -680,9 +683,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -701,25 +704,25 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D3" s="1" t="e">
-        <f ca="1">B2</f>
-        <v>#VALUE!</v>
+      <c r="D3" s="1">
+        <f>B2</f>
+        <v>46174</v>
       </c>
       <c r="E3">
         <f>$B$4</f>
         <v>0.03</v>
       </c>
-      <c r="F3" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="F3" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G3" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="G3" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D3)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H3" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="H3" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D3)</f>
-        <v>#VALUE!</v>
+      <c r="F3" s="3" cm="1">
+        <f t="array" ref="F3">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D3)</f>
+        <v>0.03</v>
+      </c>
+      <c r="G3" s="3" cm="1">
+        <f t="array" ref="G3">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D3)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" cm="1">
+        <f t="array" ref="H3">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D3)</f>
+        <v>2.9556683003227668E-2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -729,25 +732,25 @@
       <c r="B4">
         <v>0.03</v>
       </c>
-      <c r="D4" s="1" t="e">
-        <f ca="1">D3+365</f>
-        <v>#VALUE!</v>
+      <c r="D4" s="1">
+        <f>D3+365</f>
+        <v>46539</v>
       </c>
       <c r="E4">
         <f>$B$4</f>
         <v>0.03</v>
       </c>
-      <c r="F4" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="F4" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G4" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="G4" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H4" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="H4" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D4)</f>
-        <v>#VALUE!</v>
+      <c r="F4" s="3" cm="1">
+        <f t="array" ref="F4">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D4)</f>
+        <v>2.9113366006455244E-2</v>
+      </c>
+      <c r="G4" s="3" cm="1">
+        <f t="array" ref="G4">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D4)</f>
+        <v>0.97044331699677233</v>
+      </c>
+      <c r="H4" s="4" cm="1">
+        <f t="array" ref="H4">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D4)</f>
+        <v>2.9556750512494546E-2</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -757,202 +760,202 @@
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="e">
-        <f ca="1">D4+365</f>
-        <v>#VALUE!</v>
+      <c r="D5" s="1">
+        <f>D4+365</f>
+        <v>46904</v>
       </c>
       <c r="E5">
         <f>$B$4</f>
         <v>0.03</v>
       </c>
-      <c r="F5" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="F5" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G5" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="G5" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="H5" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D5)</f>
-        <v>#VALUE!</v>
+      <c r="F5" s="3" cm="1">
+        <f t="array" ref="F5">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D5)</f>
+        <v>2.8252936007527461E-2</v>
+      </c>
+      <c r="G5" s="3" cm="1">
+        <f t="array" ref="G5">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D5)</f>
+        <v>0.94176016598978107</v>
+      </c>
+      <c r="H5" s="4" cm="1">
+        <f t="array" ref="H5">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D5)</f>
+        <v>2.9556820078047608E-2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlFlatHazardRate(B2,B4,B5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D6" s="1" t="e">
-        <f ca="1">D5+365</f>
-        <v>#VALUE!</v>
+      <c r="B6" s="2" t="str" cm="1">
+        <f t="array" ref="B6">_xll.qlFlatHazardRate(B2,B4,B5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R6C2DefaultProbabilityTermStructureHandle,A</v>
+      </c>
+      <c r="D6" s="1">
+        <f>D5+365</f>
+        <v>47269</v>
       </c>
       <c r="E6">
         <f>$B$4</f>
         <v>0.03</v>
       </c>
-      <c r="F6" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="F6" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G6" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="G6" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H6" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="H6" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D6)</f>
-        <v>#VALUE!</v>
+      <c r="F6" s="3" cm="1">
+        <f t="array" ref="F6">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D6)</f>
+        <v>2.7417935558136843E-2</v>
+      </c>
+      <c r="G6" s="3" cm="1">
+        <f t="array" ref="G6">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D6)</f>
+        <v>0.91392473020694887</v>
+      </c>
+      <c r="H6" s="4" cm="1">
+        <f t="array" ref="H6">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D6)</f>
+        <v>2.9556891762529475E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D7" s="1" t="e">
-        <f ca="1">D6+365</f>
-        <v>#VALUE!</v>
+      <c r="D7" s="1">
+        <f>D6+365</f>
+        <v>47634</v>
       </c>
       <c r="E7">
         <f>$B$4</f>
         <v>0.03</v>
       </c>
-      <c r="F7" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="F7" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G7" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="G7" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H7" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="H7" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D7)</f>
-        <v>#VALUE!</v>
+      <c r="F7" s="3" cm="1">
+        <f t="array" ref="F7">_xll.qlDefaultProbabilityTermStructureDefaultDensity($B$19,D7)</f>
+        <v>2.6607613101514722E-2</v>
+      </c>
+      <c r="G7" s="3" cm="1">
+        <f t="array" ref="G7">_xll.qlDefaultProbabilityTermStructureSurvivalProbability($B$20,D7)</f>
+        <v>0.88691195587712313</v>
+      </c>
+      <c r="H7" s="4" cm="1">
+        <f t="array" ref="H7">_xll.qlDefaultProbabilityTermStructureHazardRate($B$21,D7)</f>
+        <v>3.0457109243849468E-2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultProbability(B6,B2+365)</f>
-        <v>#VALUE!</v>
+      <c r="B8" cm="1">
+        <f t="array" ref="B8">_xll.qlDefaultProbabilityTermStructureDefaultProbability(B6,B2+365)</f>
+        <v>2.9554466451491845E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultProbabilityFromTime(B6,1)</f>
-        <v>#VALUE!</v>
+      <c r="B9" cm="1">
+        <f t="array" ref="B9">_xll.qlDefaultProbabilityTermStructureDefaultProbabilityFromTime(B6,1)</f>
+        <v>2.9554466451491845E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultProbability2(B6,B2+365,B2+730)</f>
-        <v>#VALUE!</v>
+      <c r="B10" cm="1">
+        <f t="array" ref="B10">_xll.qlDefaultProbabilityTermStructureDefaultProbability2(B6,B2+365,B2+730)</f>
+        <v>2.8680999964259435E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultProbabilityFromTime2(B6,1,2)</f>
-        <v>#VALUE!</v>
+      <c r="B11" cm="1">
+        <f t="array" ref="B11">_xll.qlDefaultProbabilityTermStructureDefaultProbabilityFromTime2(B6,1,2)</f>
+        <v>2.8680999964259435E-2</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbability(B6,B2+365)</f>
-        <v>#VALUE!</v>
+      <c r="B12" cm="1">
+        <f t="array" ref="B12">_xll.qlDefaultProbabilityTermStructureSurvivalProbability(B6,B2+365)</f>
+        <v>0.97044553354850815</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlDefaultProbabilityTermStructureSurvivalProbabilityFromTime(B6,1)</f>
-        <v>#VALUE!</v>
+      <c r="B13" cm="1">
+        <f t="array" ref="B13">_xll.qlDefaultProbabilityTermStructureSurvivalProbabilityFromTime(B6,1)</f>
+        <v>0.97044553354850815</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensity(B6,B2+365)</f>
-        <v>#VALUE!</v>
+      <c r="B14" cm="1">
+        <f t="array" ref="B14">_xll.qlDefaultProbabilityTermStructureDefaultDensity(B6,B2+365)</f>
+        <v>2.9113366006455244E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlDefaultProbabilityTermStructureDefaultDensityFromTime(B6,1)</f>
-        <v>#VALUE!</v>
+      <c r="B15" cm="1">
+        <f t="array" ref="B15">_xll.qlDefaultProbabilityTermStructureDefaultDensityFromTime(B6,1)</f>
+        <v>2.9113366006455244E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate(B6,B2+365)</f>
-        <v>#VALUE!</v>
+      <c r="B16" cm="1">
+        <f t="array" ref="B16">_xll.qlDefaultProbabilityTermStructureHazardRate(B6,B2+365)</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRateFromTime(B6,1)</f>
-        <v>#VALUE!</v>
+      <c r="B17" cm="1">
+        <f t="array" ref="B17">_xll.qlDefaultProbabilityTermStructureHazardRateFromTime(B6,1)</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="e" cm="1">
-        <f t="array" aca="1" ref="B19" ca="1">_xll.qlHazardRateCurve(D3:D7,E3:E7,B5)</f>
-        <v>#VALUE!</v>
+      <c r="B19" t="str" cm="1">
+        <f t="array" ref="B19">_xll.qlHazardRateCurve(D3:D7,E3:E7,B5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R19C2DefaultProbabilityTermStructureHandle,A</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlDefaultDensityCurve(D3:D7,F3:F7,B5)</f>
-        <v>#VALUE!</v>
+      <c r="B20" t="str" cm="1">
+        <f t="array" ref="B20">_xll.qlDefaultDensityCurve(D3:D7,F3:F7,B5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R20C2DefaultProbabilityTermStructureHandle,A</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlSurvivalProbabilityCurve(D3:D7,G3:G7,B5)</f>
-        <v>#VALUE!</v>
+      <c r="B21" t="str" cm="1">
+        <f t="array" ref="B21">_xll.qlSurvivalProbabilityCurve(D3:D7,G3:G7,B5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R21C2DefaultProbabilityTermStructureHandle,A</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="B23" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlFlatForward(B2,0.03,B5)</f>
-        <v>#VALUE!</v>
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23">_xll.qlFlatForward(B2,0.03,B5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1090,17 +1093,17 @@
       <c r="A35" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C35" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D35" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
+      <c r="B35" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C35" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1127,9 +1130,9 @@
       <c r="A38" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="6" t="e">
-        <f ca="1">$B$2+B28</f>
-        <v>#VALUE!</v>
+      <c r="B38" s="6">
+        <f>$B$2+B28</f>
+        <v>46176</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -1166,360 +1169,361 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="6">
+        <f>B2</f>
+        <v>46174</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B42" ca="1">_xll.qlSpreadCdsHelper(B26,B27,B28,B29,B30,B31,B32,B33,B34,B35,B36,B37,B38,B39,B40,B41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C42" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C42" ca="1">_xll.qlSpreadCdsHelper(C26,C27,C28,C29,C30,C31,C32,C33,C34,C35)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D42" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="D42" ca="1">_xll.qlSpreadCdsHelper(D26,D27,D28,D29,D30,D31,D32,D33,D34,D35)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" t="e" cm="1">
-        <f t="array" aca="1" ref="B44" ca="1">_xll.qlDefaultProbabilityHelperQuote(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C44" t="e" cm="1">
-        <f t="array" aca="1" ref="C44" ca="1">_xll.qlDefaultProbabilityHelperQuote(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D44" t="e" cm="1">
-        <f t="array" aca="1" ref="D44" ca="1">_xll.qlDefaultProbabilityHelperQuote(D42)</f>
-        <v>#VALUE!</v>
+      <c r="B43" s="2" t="str" cm="1">
+        <f t="array" ref="B43">_xll.qlSpreadCdsHelper(B26,B27,B28,B29,B30,B31,B32,B33,B34,B35,B36,B37,B38,B39,B40,B41,B42)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R43C2SpreadCdsHelper,A</v>
+      </c>
+      <c r="C43" s="2" t="str" cm="1">
+        <f t="array" ref="C43">_xll.qlSpreadCdsHelper(C26,C27,C28,C29,C30,C31,C32,C33,C34,C35)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R43C3SpreadCdsHelper,A</v>
+      </c>
+      <c r="D43" s="2" t="str" cm="1">
+        <f t="array" ref="D43">_xll.qlSpreadCdsHelper(D26,D27,D28,D29,D30,D31,D32,D33,D34,D35)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R43C4SpreadCdsHelper,A</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B45" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C45" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C45" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D45" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D45" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(D42)</f>
-        <v>#VALUE!</v>
+        <v>50</v>
+      </c>
+      <c r="B45" cm="1">
+        <f t="array" ref="B45">_xll.qlDefaultProbabilityHelperQuote(B43)</f>
+        <v>0.03</v>
+      </c>
+      <c r="C45" cm="1">
+        <f t="array" ref="C45">_xll.qlDefaultProbabilityHelperQuote(C43)</f>
+        <v>0.03</v>
+      </c>
+      <c r="D45" cm="1">
+        <f t="array" ref="D45">_xll.qlDefaultProbabilityHelperQuote(D43)</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B46" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C46" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C46" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D46" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D46" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(D42)</f>
-        <v>#VALUE!</v>
+        <v>51</v>
+      </c>
+      <c r="B46" s="1" cm="1">
+        <f t="array" ref="B46">_xll.qlDefaultProbabilityHelperLatestDate(B43)</f>
+        <v>46559</v>
+      </c>
+      <c r="C46" s="1" cm="1">
+        <f t="array" ref="C46">_xll.qlDefaultProbabilityHelperLatestDate(C43)</f>
+        <v>46924</v>
+      </c>
+      <c r="D46" s="1" cm="1">
+        <f t="array" ref="D46">_xll.qlDefaultProbabilityHelperLatestDate(D43)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B47" ca="1">_xll.qlDefaultProbabilityHelperMaturity(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C47" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C47" ca="1">_xll.qlDefaultProbabilityHelperMaturity(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D47" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D47" ca="1">_xll.qlDefaultProbabilityHelperMaturity(D42)</f>
-        <v>#VALUE!</v>
+        <v>52</v>
+      </c>
+      <c r="B47" s="1" cm="1">
+        <f t="array" ref="B47">_xll.qlDefaultProbabilityHelperEarliestDate(B43)</f>
+        <v>46176</v>
+      </c>
+      <c r="C47" s="1" cm="1">
+        <f t="array" ref="C47">_xll.qlDefaultProbabilityHelperEarliestDate(C43)</f>
+        <v>46176</v>
+      </c>
+      <c r="D47" s="1" cm="1">
+        <f t="array" ref="D47">_xll.qlDefaultProbabilityHelperEarliestDate(D43)</f>
+        <v>46176</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B48" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C48" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C48" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D48" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D48" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(D42)</f>
-        <v>#VALUE!</v>
+        <v>53</v>
+      </c>
+      <c r="B48" s="1" cm="1">
+        <f t="array" ref="B48">_xll.qlDefaultProbabilityHelperMaturity(B43)</f>
+        <v>46559</v>
+      </c>
+      <c r="C48" s="1" cm="1">
+        <f t="array" ref="C48">_xll.qlDefaultProbabilityHelperMaturity(C43)</f>
+        <v>46924</v>
+      </c>
+      <c r="D48" s="1" cm="1">
+        <f t="array" ref="D48">_xll.qlDefaultProbabilityHelperMaturity(D43)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B49" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(B42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C49" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C49" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(C42)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D49" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D49" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(D42)</f>
-        <v>#VALUE!</v>
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" cm="1">
+        <f t="array" ref="B49">_xll.qlDefaultProbabilityHelperLatestRelevantDate(B43)</f>
+        <v>46559</v>
+      </c>
+      <c r="C49" s="1" cm="1">
+        <f t="array" ref="C49">_xll.qlDefaultProbabilityHelperLatestRelevantDate(C43)</f>
+        <v>46924</v>
+      </c>
+      <c r="D49" s="1" cm="1">
+        <f t="array" ref="D49">_xll.qlDefaultProbabilityHelperLatestRelevantDate(D43)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" t="e" cm="1">
-        <f t="array" aca="1" ref="B50" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(B42,$B$54)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C50" t="e" cm="1">
-        <f t="array" aca="1" ref="C50" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(C42,$B$54)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" t="e" cm="1">
-        <f t="array" aca="1" ref="D50" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(D42,$B$54)</f>
-        <v>#VALUE!</v>
+        <v>55</v>
+      </c>
+      <c r="B50" s="1" cm="1">
+        <f t="array" ref="B50">_xll.qlDefaultProbabilityHelperPillarDate(B43)</f>
+        <v>46559</v>
+      </c>
+      <c r="C50" s="1" cm="1">
+        <f t="array" ref="C50">_xll.qlDefaultProbabilityHelperPillarDate(C43)</f>
+        <v>46924</v>
+      </c>
+      <c r="D50" s="1" cm="1">
+        <f t="array" ref="D50">_xll.qlDefaultProbabilityHelperPillarDate(D43)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" cm="1">
+        <f t="array" ref="B51">_xll.qlDefaultProbabilityHelperImpliedQuote(B43,$B$55)</f>
+        <v>2.9999999999999843E-2</v>
+      </c>
+      <c r="C51" cm="1">
+        <f t="array" ref="C51">_xll.qlDefaultProbabilityHelperImpliedQuote(C43,$B$55)</f>
+        <v>2.9999999999999437E-2</v>
+      </c>
+      <c r="D51" cm="1">
+        <f t="array" ref="D51">_xll.qlDefaultProbabilityHelperImpliedQuote(D43,$B$55)</f>
+        <v>3.0000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>57</v>
       </c>
-      <c r="B51" t="e" cm="1">
-        <f t="array" aca="1" ref="B51" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(B42,$B$54)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C51" t="e" cm="1">
-        <f t="array" aca="1" ref="C51" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(C42,$B$54)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D51" t="e" cm="1">
-        <f t="array" aca="1" ref="D51" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(D42,$B$54)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" t="e" cm="1">
-        <f t="array" aca="1" ref="B53" ca="1">_xll.qlPiecewiseFlatHazardRate($B$2,B42:D42,$B$5)</f>
-        <v>#VALUE!</v>
+      <c r="B52" cm="1">
+        <f t="array" ref="B52">_xll.qlDefaultProbabilityHelperQuoteError(B43,$B$55)</f>
+        <v>1.5612511283791264E-16</v>
+      </c>
+      <c r="C52" cm="1">
+        <f t="array" ref="C52">_xll.qlDefaultProbabilityHelperQuoteError(C43,$B$55)</f>
+        <v>5.620504062164855E-16</v>
+      </c>
+      <c r="D52" cm="1">
+        <f t="array" ref="D52">_xll.qlDefaultProbabilityHelperQuoteError(D43,$B$55)</f>
+        <v>-3.4694469519536142E-18</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="str" cm="1">
+        <f t="array" ref="B54">_xll.qlPiecewiseFlatHazardRate($B$2,B43:D43,$B$5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R54C2DefaultProbabilityTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>14</v>
       </c>
-      <c r="B54" t="e" cm="1">
-        <f t="array" aca="1" ref="B54" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate(B53,$B$2+365)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+      <c r="B55" cm="1">
+        <f t="array" ref="B55">_xll.qlDefaultProbabilityTermStructureHazardRate(B54,$B$2+365)</f>
+        <v>5.0508366696992595E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>60</v>
-      </c>
-      <c r="B58" s="2">
-        <v>0</v>
-      </c>
-      <c r="C58" s="2">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C59" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>25</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0.01</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>26</v>
-      </c>
-      <c r="B61" s="7">
-        <v>2</v>
-      </c>
-      <c r="C61" s="2">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="B62" s="7">
+        <v>2</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="C67" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="D67" s="2">
-        <v>0.4</v>
+        <v>31</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C68" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D68" s="2" t="e">
-        <f ca="1">$B$23</f>
-        <v>#VALUE!</v>
+        <v>32</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="7">
-        <v>2</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B69" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C69" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D69" s="2" t="str">
+        <f>$B$23</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R23C2YieldTermStructureHandle,A</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>34</v>
-      </c>
-      <c r="B70" s="2" t="b">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="B70" s="7">
+        <v>2</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B71" s="2" t="b">
         <v>1</v>
@@ -1529,223 +1533,244 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>36</v>
-      </c>
-      <c r="B72" s="6" t="e">
-        <f ca="1">$B$2+B61</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
+        <v>35</v>
+      </c>
+      <c r="B72" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B73" s="6">
+        <f>$B$2+B62</f>
+        <v>46176</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="2" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>62</v>
+        <v>38</v>
+      </c>
+      <c r="B75" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>59</v>
-      </c>
-      <c r="B76" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="B76" ca="1">_xll.qlUpfrontCdsHelper(B58,B59,B60,B61,B62,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C76" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C76" ca="1">_xll.qlUpfrontCdsHelper(C58,C59,C60,C61,C62,C63,C64,C65,C66,C67,C68)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D76" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="D76" ca="1">_xll.qlUpfrontCdsHelper(D58,D59,D60,D61,D62,D63,D64,D65,D66,D67,D68)</f>
-        <v>#VALUE!</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="6">
+        <f>B2</f>
+        <v>46174</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>50</v>
-      </c>
-      <c r="B78" t="e" cm="1">
-        <f t="array" aca="1" ref="B78" ca="1">_xll.qlDefaultProbabilityHelperQuote(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C78" t="e" cm="1">
-        <f t="array" aca="1" ref="C78" ca="1">_xll.qlDefaultProbabilityHelperQuote(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D78" t="e" cm="1">
-        <f t="array" aca="1" ref="D78" ca="1">_xll.qlDefaultProbabilityHelperQuote(D76)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>51</v>
-      </c>
-      <c r="B79" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B79" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C79" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C79" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D79" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D79" ca="1">_xll.qlDefaultProbabilityHelperLatestDate(D76)</f>
-        <v>#VALUE!</v>
+        <v>59</v>
+      </c>
+      <c r="B78" s="2" t="str" cm="1">
+        <f t="array" ref="B78">_xll.qlUpfrontCdsHelper(B59,B60,B61,B62,B63,B64,B65,B66,B67,B68,B69,B70,B71,B72,B73,B74,B75,B76,B77)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R78C2UpfrontCdsHelper,A</v>
+      </c>
+      <c r="C78" s="2" t="str" cm="1">
+        <f t="array" ref="C78">_xll.qlUpfrontCdsHelper(C59,C60,C61,C62,C63,C64,C65,C66,C67,C68,C69)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R78C3UpfrontCdsHelper,A</v>
+      </c>
+      <c r="D78" s="2" t="str" cm="1">
+        <f t="array" ref="D78">_xll.qlUpfrontCdsHelper(D59,D60,D61,D62,D63,D64,D65,D66,D67,D68,D69)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R78C4UpfrontCdsHelper,A</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>52</v>
-      </c>
-      <c r="B80" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B80" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C80" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C80" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D80" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D80" ca="1">_xll.qlDefaultProbabilityHelperEarliestDate(D76)</f>
-        <v>#VALUE!</v>
+        <v>50</v>
+      </c>
+      <c r="B80" cm="1">
+        <f t="array" ref="B80">_xll.qlDefaultProbabilityHelperQuote(B78)</f>
+        <v>0</v>
+      </c>
+      <c r="C80" cm="1">
+        <f t="array" ref="C80">_xll.qlDefaultProbabilityHelperQuote(C78)</f>
+        <v>0</v>
+      </c>
+      <c r="D80" cm="1">
+        <f t="array" ref="D80">_xll.qlDefaultProbabilityHelperQuote(D78)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>53</v>
-      </c>
-      <c r="B81" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B81" ca="1">_xll.qlDefaultProbabilityHelperMaturity(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C81" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C81" ca="1">_xll.qlDefaultProbabilityHelperMaturity(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D81" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D81" ca="1">_xll.qlDefaultProbabilityHelperMaturity(D76)</f>
-        <v>#VALUE!</v>
+        <v>51</v>
+      </c>
+      <c r="B81" s="1" cm="1">
+        <f t="array" ref="B81">_xll.qlDefaultProbabilityHelperLatestDate(B78)</f>
+        <v>46560</v>
+      </c>
+      <c r="C81" s="1" cm="1">
+        <f t="array" ref="C81">_xll.qlDefaultProbabilityHelperLatestDate(C78)</f>
+        <v>46924</v>
+      </c>
+      <c r="D81" s="1" cm="1">
+        <f t="array" ref="D81">_xll.qlDefaultProbabilityHelperLatestDate(D78)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>54</v>
-      </c>
-      <c r="B82" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B82" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C82" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C82" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D82" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D82" ca="1">_xll.qlDefaultProbabilityHelperLatestRelevantDate(D76)</f>
-        <v>#VALUE!</v>
+        <v>52</v>
+      </c>
+      <c r="B82" s="1" cm="1">
+        <f t="array" ref="B82">_xll.qlDefaultProbabilityHelperEarliestDate(B78)</f>
+        <v>46176</v>
+      </c>
+      <c r="C82" s="1" cm="1">
+        <f t="array" ref="C82">_xll.qlDefaultProbabilityHelperEarliestDate(C78)</f>
+        <v>46174</v>
+      </c>
+      <c r="D82" s="1" cm="1">
+        <f t="array" ref="D82">_xll.qlDefaultProbabilityHelperEarliestDate(D78)</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>55</v>
-      </c>
-      <c r="B83" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B83" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(B76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C83" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C83" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(C76)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D83" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D83" ca="1">_xll.qlDefaultProbabilityHelperPillarDate(D76)</f>
-        <v>#VALUE!</v>
+        <v>53</v>
+      </c>
+      <c r="B83" s="1" cm="1">
+        <f t="array" ref="B83">_xll.qlDefaultProbabilityHelperMaturity(B78)</f>
+        <v>46560</v>
+      </c>
+      <c r="C83" s="1" cm="1">
+        <f t="array" ref="C83">_xll.qlDefaultProbabilityHelperMaturity(C78)</f>
+        <v>46924</v>
+      </c>
+      <c r="D83" s="1" cm="1">
+        <f t="array" ref="D83">_xll.qlDefaultProbabilityHelperMaturity(D78)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>56</v>
-      </c>
-      <c r="B84" t="e" cm="1">
-        <f t="array" aca="1" ref="B84" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(B76,$B$88)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C84" t="e" cm="1">
-        <f t="array" aca="1" ref="C84" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(C76,$B$88)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D84" t="e" cm="1">
-        <f t="array" aca="1" ref="D84" ca="1">_xll.qlDefaultProbabilityHelperImpliedQuote(D76,$B$88)</f>
-        <v>#VALUE!</v>
+        <v>54</v>
+      </c>
+      <c r="B84" s="1" cm="1">
+        <f t="array" ref="B84">_xll.qlDefaultProbabilityHelperLatestRelevantDate(B78)</f>
+        <v>46560</v>
+      </c>
+      <c r="C84" s="1" cm="1">
+        <f t="array" ref="C84">_xll.qlDefaultProbabilityHelperLatestRelevantDate(C78)</f>
+        <v>46924</v>
+      </c>
+      <c r="D84" s="1" cm="1">
+        <f t="array" ref="D84">_xll.qlDefaultProbabilityHelperLatestRelevantDate(D78)</f>
+        <v>48019</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>57</v>
-      </c>
-      <c r="B85" t="e" cm="1">
-        <f t="array" aca="1" ref="B85" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(B76,$B$88)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C85" t="e" cm="1">
-        <f t="array" aca="1" ref="C85" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(C76,$B$88)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D85" t="e" cm="1">
-        <f t="array" aca="1" ref="D85" ca="1">_xll.qlDefaultProbabilityHelperQuoteError(D76,$B$88)</f>
-        <v>#VALUE!</v>
+        <v>55</v>
+      </c>
+      <c r="B85" s="1" cm="1">
+        <f t="array" ref="B85">_xll.qlDefaultProbabilityHelperPillarDate(B78)</f>
+        <v>46560</v>
+      </c>
+      <c r="C85" s="1" cm="1">
+        <f t="array" ref="C85">_xll.qlDefaultProbabilityHelperPillarDate(C78)</f>
+        <v>46924</v>
+      </c>
+      <c r="D85" s="1" cm="1">
+        <f t="array" ref="D85">_xll.qlDefaultProbabilityHelperPillarDate(D78)</f>
+        <v>48019</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>56</v>
+      </c>
+      <c r="B86" cm="1">
+        <f t="array" ref="B86">_xll.qlDefaultProbabilityHelperImpliedQuote(B78,$B$90)</f>
+        <v>7.2176360232676936E-16</v>
+      </c>
+      <c r="C86" cm="1">
+        <f t="array" ref="C86">_xll.qlDefaultProbabilityHelperImpliedQuote(C78,$B$90)</f>
+        <v>2.8865798640254071E-17</v>
+      </c>
+      <c r="D86" cm="1">
+        <f t="array" ref="D86">_xll.qlDefaultProbabilityHelperImpliedQuote(D78,$B$90)</f>
+        <v>-8.8817841970012525E-18</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>57</v>
+      </c>
+      <c r="B87" cm="1">
+        <f t="array" ref="B87">_xll.qlDefaultProbabilityHelperQuoteError(B78,$B$90)</f>
+        <v>-7.2176360232676936E-16</v>
+      </c>
+      <c r="C87" cm="1">
+        <f t="array" ref="C87">_xll.qlDefaultProbabilityHelperQuoteError(C78,$B$90)</f>
+        <v>-2.8865798640254071E-17</v>
+      </c>
+      <c r="D87" cm="1">
+        <f t="array" ref="D87">_xll.qlDefaultProbabilityHelperQuoteError(D78,$B$90)</f>
+        <v>8.8817841970012525E-18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>58</v>
       </c>
-      <c r="B87" t="e" cm="1">
-        <f t="array" aca="1" ref="B87" ca="1">_xll.qlPiecewiseFlatHazardRate($B$2,B76:D76,$B$5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="B89" t="str" cm="1">
+        <f t="array" ref="B89">_xll.qlPiecewiseFlatHazardRate($B$2,B78:D78,$B$5)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R89C2DefaultProbabilityTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>14</v>
       </c>
-      <c r="B88" t="e" cm="1">
-        <f t="array" aca="1" ref="B88" ca="1">_xll.qlDefaultProbabilityTermStructureHazardRate(B87,$B$2+365)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+      <c r="B90" cm="1">
+        <f t="array" ref="B90">_xll.qlDefaultProbabilityTermStructureHazardRate(B89,$B$2+365)</f>
+        <v>1.67935743663419E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
         <v>63</v>
       </c>
-      <c r="B91" t="e" cm="1">
-        <f t="array" aca="1" ref="B91" ca="1">_xll.qlRiskyBondEngine(B87,B67,B68)</f>
-        <v>#VALUE!</v>
+      <c r="B93" t="str" cm="1">
+        <f t="array" ref="B93">_xll.qlRiskyBondEngine(B89,B68,B69)</f>
+        <v>欣[test_defaultprobability.xlsx]Sheet1!R93C2RiskyBondEngine,A</v>
       </c>
     </row>
   </sheetData>
